--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlLevel.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlLevel.xlsx
@@ -134,7 +134,7 @@
     <t>331,327,243,163,176,256,251,231,211,191,171,87,91</t>
   </si>
   <si>
-    <t>0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,1,2,1,0,1,1,0,0,0,0,0,0,0,0,0,0,0,1,0,0,2,2,2,0,0,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,0,0,1,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,0,0,1,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,0,0,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,0,0,0,0,0,0,0,1,0,0,0,0,0,0,0,0,0,0,0,1,1,0,1,1,1,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</t>
+    <t>1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,1,1,1,1,1,0,0,0,0,1,1,0,0,0,0,0,0,0,0,2,1,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,2,2,2,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,2,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,2,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,2,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1</t>
   </si>
   <si>
     <t>247,171</t>
@@ -228,7 +228,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
+    <numFmt numFmtId="0" formatCode="General"/>
     <numFmt numFmtId="0" formatCode="General"/>
     <numFmt numFmtId="0" formatCode="General"/>
     <numFmt numFmtId="0" formatCode="General"/>

--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlLevel.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlLevel.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="BrawlLevel" sheetId="1" state="visible" r:id="rId3"/>
@@ -116,34 +116,34 @@
     <t>389,10</t>
   </si>
   <si>
+    <t>Packages/cn.etetet.brawl/Bundles/Scenes/BrawlArena_Train.unity</t>
+  </si>
+  <si>
+    <t>0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,1,1,1,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,0,0,0,2,1,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,2,1,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,2,1,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,0,0,0,2,2,0,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,1,1,1,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>101,101,201,201,201,201,201,201,201,201,201,201,201</t>
+  </si>
+  <si>
+    <t>331,327,243,163,176,256,251,231,211,191,171,87,91</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Packages/cn.etetet.brawl/Bundles/Scenes/BrawlArena_Train.unity</t>
-  </si>
-  <si>
-    <t>0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,1,1,1,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,0,0,0,2,1,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,2,1,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,2,1,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,0,0,0,2,2,0,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,1,1,1,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</t>
-  </si>
-  <si>
-    <t>209</t>
-  </si>
-  <si>
-    <t>101,101,201,201,201,201,201,201,201,201,201,201,201</t>
-  </si>
-  <si>
-    <t>331,327,243,163,176,256,251,231,211,191,171,87,91</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,1,1,1,1,1,0,0,0,0,1,1,0,0,0,0,0,0,0,0,2,1,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,2,2,2,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,2,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,2,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,2,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1</t>
-  </si>
-  <si>
-    <t>247,171</t>
-  </si>
-  <si>
-    <t>201,201,101,101,101,101,101,101,101,101</t>
-  </si>
-  <si>
-    <t>251,167,245,253,287,291,127,131,165,173</t>
+    <t>0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,0,0,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,0,0,1,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,1,0,0,1,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,1,0,0,1,1,1,1,1,0,0,0,0,0,0,0,0,0,0,1,1,1,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,0,0,0,0,0,0,0,0,2,2,2,2,2,0,0,2,2,2,2,2,2,2,2,2,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,2,2,2,2,2,2,2,2,2,0,0,2,2,2,2,2,0,0,0,0,0,0,0,0,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</t>
+  </si>
+  <si>
+    <t>97,100</t>
+  </si>
+  <si>
+    <t>101,101,101,201,201,101,101,101,101,101,101,101,101,101,101,101,101,101,201,201,201,201,201,101,101,101,101,101,101,101,101,101,101,201</t>
+  </si>
+  <si>
+    <t>269,277,315,190,191,270,271,272,278,279,280,316,317,318,319,320,321,322,185,184,183,182,189,160,138,116,94,72,169,147,125,103,81,188</t>
   </si>
   <si>
     <t>Description</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">赏金猎人 </t>
   </si>
   <si>
-    <t>Wall_Tile_Wights</t>
+    <t>Wall_Tile_X</t>
   </si>
   <si>
     <t>Grass_Tile_A Bounty</t>
@@ -228,10 +228,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
-    <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="0" formatCode="General"/>
+  <numFmts count="3">
     <numFmt numFmtId="0" formatCode="General"/>
     <numFmt numFmtId="0" formatCode="General"/>
     <numFmt numFmtId="164" formatCode="General"/>
@@ -320,13 +317,14 @@
     <xf numFmtId="9" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
     <xf numFmtId="164" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" borderId="0" applyBorder="1" applyProtection="1" applyAlignment="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1"/>
     <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1"/>
     <xf numFmtId="164" applyNumberFormat="1" fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
     <xf numFmtId="164" applyNumberFormat="1" fontId="4" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
     <xf numFmtId="164" applyNumberFormat="1" fontId="4" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
     <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1"/>
     <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -766,9 +764,6 @@
       </c>
     </row>
     <row r="7" ht="15">
-      <c r="A7" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="B7" s="1">
         <v>10101</v>
       </c>
@@ -779,7 +774,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7" s="1">
         <v>20</v>
@@ -788,21 +783,21 @@
         <v>20</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="J7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="0" t="s">
+      <c r="K7" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="K7" s="0" t="s">
+    </row>
+    <row r="8" ht="15">
+      <c r="A8" s="1" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="B8" s="1">
         <v>10201</v>
@@ -817,10 +812,10 @@
         <v>28</v>
       </c>
       <c r="F8" s="1">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G8" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>37</v>
@@ -828,10 +823,10 @@
       <c r="I8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J8" s="0" t="s">
+      <c r="J8" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K8" s="0" t="s">
+      <c r="K8" s="6" t="s">
         <v>40</v>
       </c>
     </row>
@@ -856,7 +851,7 @@
   <cols>
     <col min="1" max="2" width="16" customWidth="1" style="1"/>
     <col min="3" max="3" width="26" customWidth="1" style="1"/>
-    <col min="4" max="8" width="26" customWidth="1" style="6"/>
+    <col min="4" max="8" width="26" customWidth="1" style="7"/>
     <col min="9" max="9" width="26" customWidth="1" style="1"/>
     <col min="10" max="10" width="8.68" customWidth="1" style="1"/>
   </cols>
@@ -871,19 +866,19 @@
       <c r="C1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -897,19 +892,19 @@
       <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -921,19 +916,19 @@
       <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -947,19 +942,19 @@
       <c r="C4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>53</v>
       </c>
     </row>
@@ -970,10 +965,10 @@
       <c r="C5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="11" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1016,10 +1011,10 @@
       <c r="C10" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="11" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1030,10 +1025,10 @@
       <c r="C11" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="11" t="s">
         <v>66</v>
       </c>
     </row>

--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlLevel.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlLevel.xlsx
@@ -5,13 +5,13 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="BrawlLevel" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="BrawlLevelStyle" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001" fullCalcOnLoad="1" fullPrecision="1"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -21,180 +21,177 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>ModeId</t>
-  </si>
-  <si>
-    <t>StyleId</t>
-  </si>
-  <si>
-    <t>SceneAsset</t>
-  </si>
-  <si>
-    <t>RowCount</t>
-  </si>
-  <si>
-    <t>ColumnCount</t>
-  </si>
-  <si>
-    <t>MapGrid</t>
-  </si>
-  <si>
-    <t>SpawnPoints</t>
-  </si>
-  <si>
-    <t>NPCIds</t>
-  </si>
-  <si>
-    <t>NPCPoints</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>(array#sep=,),int</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>关卡 ID</t>
-  </si>
-  <si>
-    <t>所属玩法 ID</t>
-  </si>
-  <si>
-    <t>关卡表现 ID</t>
-  </si>
-  <si>
-    <t>客户端场景资源</t>
-  </si>
-  <si>
-    <t>网格行数</t>
-  </si>
-  <si>
-    <t>网格列数</t>
-  </si>
-  <si>
-    <t>格子类型数组</t>
-  </si>
-  <si>
-    <t>玩家出生格索引</t>
-  </si>
-  <si>
-    <t>NPC 配置 ID（与 NPCPoints 一一对应）</t>
-  </si>
-  <si>
-    <t>NPC 所在格子索引（每格最多一个）</t>
-  </si>
-  <si>
-    <t>Packages/cn.etetet.brawl/Bundles/Scenes/BrawlArena_Forest.unity</t>
-  </si>
-  <si>
-    <t>0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,2,1,1,1,1,1,2,2,1,1,1,1,1,2,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,2,1,1,1,1,1,2,2,1,1,1,1,1,2,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</t>
-  </si>
-  <si>
-    <t>389,10</t>
-  </si>
-  <si>
-    <t>Packages/cn.etetet.brawl/Bundles/Scenes/BrawlArena_Train.unity</t>
-  </si>
-  <si>
-    <t>0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,1,1,1,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,0,0,0,2,1,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,2,1,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,2,1,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,0,0,0,2,2,0,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,1,1,1,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</t>
-  </si>
-  <si>
-    <t>209</t>
-  </si>
-  <si>
-    <t>101,101,201,201,201,201,201,201,201,201,201,201,201</t>
-  </si>
-  <si>
-    <t>331,327,243,163,176,256,251,231,211,191,171,87,91</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,0,0,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,0,0,1,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,1,0,0,1,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,1,0,0,1,1,1,1,1,0,0,0,0,0,0,0,0,0,0,1,1,1,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,0,0,0,0,0,0,0,0,2,2,2,2,2,0,0,2,2,2,2,2,2,2,2,2,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,2,2,2,2,2,2,2,2,2,0,0,2,2,2,2,2,0,0,0,0,0,0,0,0,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</t>
-  </si>
-  <si>
-    <t>97,100</t>
-  </si>
-  <si>
-    <t>101,101,101,201,201,101,101,101,101,101,101,101,101,101,101,101,101,101,201,201,201,201,201,101,101,101,101,101,101,101,101,101,101,201</t>
-  </si>
-  <si>
-    <t>269,277,315,190,191,270,271,272,278,279,280,316,317,318,319,320,321,322,185,184,183,182,189,160,138,116,94,72,169,147,125,103,81,188</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>ModelPath1</t>
-  </si>
-  <si>
-    <t>ModelPath2</t>
-  </si>
-  <si>
-    <t>ModelPath3</t>
-  </si>
-  <si>
-    <t>ModelPath4</t>
-  </si>
-  <si>
-    <t>ModelPath5</t>
-  </si>
-  <si>
-    <t>风格 ID</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>模型路径1</t>
-  </si>
-  <si>
-    <t>模型路径2</t>
-  </si>
-  <si>
-    <t>模型路径3</t>
-  </si>
-  <si>
-    <t>模型路径4</t>
-  </si>
-  <si>
-    <t>模型路径5</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="66">
+  <si>
+    <t xml:space="preserve">##var</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ModeId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StyleId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SceneAsset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RowCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColumnCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MapGrid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpawnPoints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPCIds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPCPoints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(array#sep=,),int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##</t>
+  </si>
+  <si>
+    <t xml:space="preserve">关卡 ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">所属玩法 ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">关卡表现 ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">客户端场景资源</t>
+  </si>
+  <si>
+    <t xml:space="preserve">网格行数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">网格列数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">格子类型数组</t>
+  </si>
+  <si>
+    <t xml:space="preserve">玩家出生格索引</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPC 配置 ID（与 NPCPoints 一一对应）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPC 所在格子索引（每格最多一个）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packages/cn.etetet.brawl/Bundles/Scenes/BrawlArena_Forest.unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,2,1,1,1,1,1,2,2,1,1,1,1,1,2,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,2,1,1,1,1,1,2,2,1,1,1,1,1,2,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">389,10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packages/cn.etetet.brawl/Bundles/Scenes/BrawlArena_Train.unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,1,1,1,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,0,0,0,2,1,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,2,1,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,2,1,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,0,0,0,2,2,0,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,1,1,1,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101,101,201,201,201,201,201,201,201,201,201,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331,327,243,163,176,256,231,211,191,87,91,212,172,252,254,214,174,132,134,292,294,290,288,250,248,168,170,130,128,123,283,296,136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,0,0,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,0,0,1,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,1,0,0,1,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,1,0,0,1,1,1,1,1,0,0,0,0,0,0,0,0,0,0,1,1,1,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,0,0,0,0,0,0,0,0,2,2,2,2,2,0,0,2,2,2,2,2,2,2,2,2,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,2,2,2,2,2,2,2,2,2,0,0,2,2,2,2,2,0,0,0,0,0,0,0,0,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97,100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101,101,101,201,201,101,101,101,101,101,101,101,101,101,101,101,101,101,201,201,201,201,201,101,101,101,101,101,101,101,101,101,101,201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">269,277,315,190,191,270,271,272,278,279,280,316,317,318,319,320,321,322,185,184,183,182,189,160,138,116,94,72,169,147,125,103,81,188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ModelPath1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ModelPath2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ModelPath3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ModelPath4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ModelPath5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">风格 ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">描述</t>
+  </si>
+  <si>
+    <t xml:space="preserve">模型路径1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">模型路径2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">模型路径3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">模型路径4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">模型路径5</t>
   </si>
   <si>
     <t xml:space="preserve">赏金猎人 </t>
   </si>
   <si>
-    <t>Wall_Tile_X</t>
-  </si>
-  <si>
-    <t>Grass_Tile_A Bounty</t>
-  </si>
-  <si>
-    <t>乱斗足球</t>
+    <t xml:space="preserve">Wall_Tile_X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grass_Tile_A Bounty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">乱斗足球</t>
   </si>
   <si>
     <t xml:space="preserve">宝石争霸 </t>
@@ -206,39 +203,47 @@
     <t xml:space="preserve">热区争夺 </t>
   </si>
   <si>
-    <t>荒野决斗——沙漠</t>
-  </si>
-  <si>
-    <t>Wall_Tile_Desert</t>
-  </si>
-  <si>
-    <t>Grass_Tile_A Desert</t>
+    <t xml:space="preserve">荒野决斗——沙漠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wall_Tile_Desert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grass_Tile_A Desert</t>
   </si>
   <si>
     <t xml:space="preserve">荒野决斗——夜晚 </t>
   </si>
   <si>
-    <t>Wall_Tile_Block1</t>
-  </si>
-  <si>
-    <t>Grass_Tile_Night</t>
+    <t xml:space="preserve">Wall_Tile_Block1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grass_Tile_Night</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="0" formatCode="General"/>
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Noto Sans SC"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
@@ -252,7 +257,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF222222"/>
       <name val="Microsoft YaHei"/>
@@ -300,7 +305,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="1" diagonalDown="1">
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -308,47 +313,93 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="7">
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="1" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" borderId="0" applyBorder="1" applyProtection="1" applyAlignment="1"/>
+  <cellStyleXfs count="21">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="4" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="4" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="4" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="4" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
-    <cellStyle name="Normal" xfId="6"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Normal" xfId="20"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -583,20 +634,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr xr2 ">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="4" width="16" customWidth="1" style="1"/>
-    <col min="5" max="5" width="26" customWidth="1" style="1"/>
-    <col min="6" max="7" width="18" customWidth="1" style="1"/>
-    <col min="8" max="9" width="25" customWidth="1" style="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="25"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -631,7 +682,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -666,7 +717,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" ht="26" customHeight="1">
+    <row r="3" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
@@ -685,7 +736,7 @@
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
     </row>
-    <row r="4" ht="26" customHeight="1">
+    <row r="4" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>17</v>
       </c>
@@ -720,40 +771,40 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" ht="15">
-      <c r="B5" s="1">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="n">
         <v>101</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="1" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="6" ht="15">
-      <c r="B6" s="1">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="n">
         <v>10001</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H6" s="5" t="s">
@@ -763,23 +814,23 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" ht="15">
-      <c r="B7" s="1">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="n">
         <v>10101</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="1" t="n">
         <v>101</v>
       </c>
-      <c r="D7" s="1">
-        <v>1</v>
+      <c r="D7" s="1" t="n">
+        <v>6</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H7" s="5" t="s">
@@ -795,39 +846,36 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" ht="15">
-      <c r="A8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="1">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="n">
         <v>10201</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="1" t="n">
         <v>102</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="1" t="n">
         <v>22</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="J8" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="K8" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -842,21 +890,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr xr2 ">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="2" width="16" customWidth="1" style="1"/>
-    <col min="3" max="3" width="26" customWidth="1" style="1"/>
-    <col min="4" max="8" width="26" customWidth="1" style="7"/>
-    <col min="9" max="9" width="26" customWidth="1" style="1"/>
-    <col min="10" max="10" width="8.68" customWidth="1" style="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="4" style="7" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.68"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -864,25 +912,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
+    </row>
+    <row r="2" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -908,7 +956,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="26" customHeight="1">
+    <row r="3" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
@@ -932,104 +980,104 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" ht="26" customHeight="1">
+    <row r="4" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="G4" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="H4" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H4" s="10" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="5" ht="12.8">
-      <c r="B5" s="1">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="11" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" ht="14.9" customHeight="1">
-      <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1" t="s">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
-      <c r="B7" s="1">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1" t="s">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="8" ht="12.8">
-      <c r="B8" s="1">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1" t="s">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="9" ht="12.8">
-      <c r="B9" s="1">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1" t="s">
+    <row r="10" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="10" ht="14.15" customHeight="1">
-      <c r="B10" s="1">
-        <v>6</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="E10" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="11" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="11" ht="12.8">
-      <c r="B11" s="1">
-        <v>7</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="E11" s="11" t="s">
         <v>65</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1041,9 +1089,4 @@
     <oddFooter>&amp;C&amp;"Times New Roman"&amp;12页 &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
-For more information about EPPlus, see https://epplussoftware.com/
-
 </file>
--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlLevel.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlLevel.xlsx
@@ -11,7 +11,7 @@
     <sheet name="BrawlLevel" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="BrawlLevelStyle" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -21,177 +21,177 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="66">
-  <si>
-    <t xml:space="preserve">##var</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ModeId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StyleId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SceneAsset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RowCount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColumnCount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MapGrid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpawnPoints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPCIds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPCPoints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">##type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">int</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(array#sep=,),int</t>
-  </si>
-  <si>
-    <t xml:space="preserve">##group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">##</t>
-  </si>
-  <si>
-    <t xml:space="preserve">关卡 ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">所属玩法 ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">关卡表现 ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">客户端场景资源</t>
-  </si>
-  <si>
-    <t xml:space="preserve">网格行数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">网格列数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">格子类型数组</t>
-  </si>
-  <si>
-    <t xml:space="preserve">玩家出生格索引</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPC 配置 ID（与 NPCPoints 一一对应）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPC 所在格子索引（每格最多一个）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Packages/cn.etetet.brawl/Bundles/Scenes/BrawlArena_Forest.unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,2,1,1,1,1,1,2,2,1,1,1,1,1,2,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,2,1,1,1,1,1,2,2,1,1,1,1,1,2,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">389,10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Packages/cn.etetet.brawl/Bundles/Scenes/BrawlArena_Train.unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,1,1,1,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,0,0,0,2,1,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,2,1,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,2,1,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,0,0,0,2,2,0,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,1,1,1,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101,101,201,201,201,201,201,201,201,201,201,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331,327,243,163,176,256,231,211,191,87,91,212,172,252,254,214,174,132,134,292,294,290,288,250,248,168,170,130,128,123,283,296,136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,0,0,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,0,0,1,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,1,0,0,1,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,1,0,0,1,1,1,1,1,0,0,0,0,0,0,0,0,0,0,1,1,1,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,0,0,0,0,0,0,0,0,2,2,2,2,2,0,0,2,2,2,2,2,2,2,2,2,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,2,2,2,2,2,2,2,2,2,0,0,2,2,2,2,2,0,0,0,0,0,0,0,0,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97,100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101,101,101,201,201,101,101,101,101,101,101,101,101,101,101,101,101,101,201,201,201,201,201,101,101,101,101,101,101,101,101,101,101,201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">269,277,315,190,191,270,271,272,278,279,280,316,317,318,319,320,321,322,185,184,183,182,189,160,138,116,94,72,169,147,125,103,81,188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ModelPath1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ModelPath2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ModelPath3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ModelPath4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ModelPath5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">风格 ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">描述</t>
-  </si>
-  <si>
-    <t xml:space="preserve">模型路径1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">模型路径2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">模型路径3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">模型路径4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">模型路径5</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>ModeId</t>
+  </si>
+  <si>
+    <t>StyleId</t>
+  </si>
+  <si>
+    <t>SceneAsset</t>
+  </si>
+  <si>
+    <t>RowCount</t>
+  </si>
+  <si>
+    <t>ColumnCount</t>
+  </si>
+  <si>
+    <t>MapGrid</t>
+  </si>
+  <si>
+    <t>SpawnPoints</t>
+  </si>
+  <si>
+    <t>NPCIds</t>
+  </si>
+  <si>
+    <t>NPCPoints</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>(array#sep=,),int</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>关卡 ID</t>
+  </si>
+  <si>
+    <t>所属玩法 ID</t>
+  </si>
+  <si>
+    <t>关卡表现 ID</t>
+  </si>
+  <si>
+    <t>客户端场景资源</t>
+  </si>
+  <si>
+    <t>网格行数</t>
+  </si>
+  <si>
+    <t>网格列数</t>
+  </si>
+  <si>
+    <t>格子类型数组</t>
+  </si>
+  <si>
+    <t>玩家出生格索引</t>
+  </si>
+  <si>
+    <t>NPC 配置 ID（与 NPCPoints 一一对应）</t>
+  </si>
+  <si>
+    <t>NPC 所在格子索引（每格最多一个）</t>
+  </si>
+  <si>
+    <t>Packages/cn.etetet.brawl/Bundles/Scenes/BrawlArena_Forest.unity</t>
+  </si>
+  <si>
+    <t>0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,2,1,1,1,1,1,2,2,1,1,1,1,1,2,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,2,1,1,1,1,1,2,2,1,1,1,1,1,2,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</t>
+  </si>
+  <si>
+    <t>389,10</t>
+  </si>
+  <si>
+    <t>Packages/cn.etetet.brawl/Bundles/Scenes/BrawlArena_Train.unity</t>
+  </si>
+  <si>
+    <t>0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,1,1,1,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,0,0,0,2,1,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,2,1,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,2,1,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,0,0,0,2,2,0,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,1,1,1,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>101,101,201,201,201,201,201,201,201,201,201,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401</t>
+  </si>
+  <si>
+    <t>331,327,243,163,176,256,231,211,191,87,91,212,172,252,254,214,174,132,134,292,294,290,288,250,248,168,170,130,128,123,283,296,136</t>
+  </si>
+  <si>
+    <t>0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,0,0,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,0,0,1,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,1,0,0,1,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,1,0,0,1,1,1,1,1,0,0,0,0,0,0,0,0,0,0,1,1,1,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,0,0,0,0,0,0,0,0,2,2,2,2,2,0,0,2,2,2,2,2,2,2,2,2,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,2,2,2,2,2,2,2,2,2,0,0,2,2,2,2,2,0,0,0,0,0,0,0,0,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</t>
+  </si>
+  <si>
+    <t>97,100</t>
+  </si>
+  <si>
+    <t>101,101,101,201,201,101,101,101,101,101,101,101,101,101,101,101,101,101,201,201,201,201,201,101,101,101,101,101,101,101,101,101,101,201</t>
+  </si>
+  <si>
+    <t>269,277,315,190,191,270,271,272,278,279,280,316,317,318,319,320,321,322,185,184,183,182,189,160,138,116,94,72,169,147,125,103,81,188</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>ModelPath1</t>
+  </si>
+  <si>
+    <t>ModelPath2</t>
+  </si>
+  <si>
+    <t>ModelPath3</t>
+  </si>
+  <si>
+    <t>ModelPath4</t>
+  </si>
+  <si>
+    <t>ModelPath5</t>
+  </si>
+  <si>
+    <t>风格 ID</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>模型路径1</t>
+  </si>
+  <si>
+    <t>模型路径2</t>
+  </si>
+  <si>
+    <t>模型路径3</t>
+  </si>
+  <si>
+    <t>模型路径4</t>
+  </si>
+  <si>
+    <t>模型路径5</t>
   </si>
   <si>
     <t xml:space="preserve">赏金猎人 </t>
   </si>
   <si>
-    <t xml:space="preserve">Wall_Tile_X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grass_Tile_A Bounty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">乱斗足球</t>
+    <t>Wall_Tile_X</t>
+  </si>
+  <si>
+    <t>Grass_Tile_A Bounty</t>
+  </si>
+  <si>
+    <t>乱斗足球</t>
   </si>
   <si>
     <t xml:space="preserve">宝石争霸 </t>
@@ -203,47 +203,39 @@
     <t xml:space="preserve">热区争夺 </t>
   </si>
   <si>
-    <t xml:space="preserve">荒野决斗——沙漠</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wall_Tile_Desert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grass_Tile_A Desert</t>
+    <t>荒野决斗——沙漠</t>
+  </si>
+  <si>
+    <t>Wall_Tile_Desert</t>
+  </si>
+  <si>
+    <t>Grass_Tile_A Desert</t>
   </si>
   <si>
     <t xml:space="preserve">荒野决斗——夜晚 </t>
   </si>
   <si>
-    <t xml:space="preserve">Wall_Tile_Block1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grass_Tile_Night</t>
+    <t>Wall_Tile_Block1</t>
+  </si>
+  <si>
+    <t>Grass_Tile_Night</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="0" formatCode="General"/>
+    <numFmt numFmtId="0" formatCode="General"/>
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Noto Sans SC"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
@@ -257,7 +249,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF222222"/>
       <name val="Microsoft YaHei"/>
@@ -305,7 +297,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border diagonalUp="1" diagonalDown="1">
       <left/>
       <right/>
       <top/>
@@ -313,93 +305,47 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellStyleXfs count="7">
+    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="1" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="43" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" borderId="0" applyBorder="1" applyProtection="1" applyAlignment="1"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="4" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="4" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="4" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="4" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Normal" xfId="20"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+    <cellStyle name="Normal" xfId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -634,20 +580,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr xr2 ">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="25"/>
+    <col min="1" max="4" width="16" customWidth="1" style="1"/>
+    <col min="5" max="5" width="26" customWidth="1" style="1"/>
+    <col min="6" max="7" width="18" customWidth="1" style="1"/>
+    <col min="8" max="9" width="25" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -682,7 +628,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -717,7 +663,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" ht="26" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
@@ -736,7 +682,7 @@
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
     </row>
-    <row r="4" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>17</v>
       </c>
@@ -771,40 +717,40 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="n">
+    <row r="5" ht="15">
+      <c r="B5" s="1">
         <v>101</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="1">
         <v>20</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="n">
+    <row r="6" ht="15">
+      <c r="B6" s="1">
         <v>10001</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="1">
         <v>100</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="1">
         <v>1</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="1">
         <v>20</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="1">
         <v>20</v>
       </c>
       <c r="H6" s="5" t="s">
@@ -814,23 +760,23 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="n">
+    <row r="7" ht="15">
+      <c r="B7" s="1">
         <v>10101</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="1">
         <v>101</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="1">
         <v>6</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7" s="1">
         <v>20</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="1">
         <v>20</v>
       </c>
       <c r="H7" s="5" t="s">
@@ -846,23 +792,23 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="n">
+    <row r="8" ht="15">
+      <c r="B8" s="1">
         <v>10201</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="1">
         <v>102</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="1">
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="F8" s="1">
         <v>35</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="1">
         <v>22</v>
       </c>
       <c r="H8" s="1" t="s">
@@ -876,6 +822,38 @@
       </c>
       <c r="K8" s="6" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="9" ht="15">
+      <c r="B9" s="1">
+        <v>10202</v>
+      </c>
+      <c r="C9" s="1">
+        <v>102</v>
+      </c>
+      <c r="D9" s="1">
+        <v>6</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="1">
+        <v>20</v>
+      </c>
+      <c r="G9" s="1">
+        <v>20</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -890,21 +868,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr xr2 ">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="4" style="7" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.68"/>
+    <col min="1" max="2" width="16" customWidth="1" style="1"/>
+    <col min="3" max="3" width="26" customWidth="1" style="1"/>
+    <col min="4" max="8" width="26" customWidth="1" style="7"/>
+    <col min="9" max="9" width="26" customWidth="1" style="1"/>
+    <col min="10" max="10" width="8.68" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -930,7 +908,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -956,7 +934,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" ht="26" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
@@ -980,7 +958,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>17</v>
       </c>
@@ -1006,8 +984,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="n">
+    <row r="5" ht="12.8">
+      <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1020,40 +998,40 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="n">
+    <row r="6" ht="14.9" customHeight="1">
+      <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="n">
+    <row r="7" ht="12.8">
+      <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="n">
+    <row r="8" ht="12.8">
+      <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="n">
+    <row r="9" ht="12.8">
+      <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="n">
+    <row r="10" ht="14.15" customHeight="1">
+      <c r="B10" s="1">
         <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1066,8 +1044,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="n">
+    <row r="11" ht="12.8">
+      <c r="B11" s="1">
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -1089,4 +1067,9 @@
     <oddFooter>&amp;C&amp;"Times New Roman"&amp;12页 &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>
--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlLevel.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlLevel.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t>##var</t>
   </si>
@@ -116,19 +116,22 @@
     <t>389,10</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>Packages/cn.etetet.brawl/Bundles/Scenes/BrawlArena_Train.unity</t>
   </si>
   <si>
-    <t>0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,1,1,1,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,0,0,0,2,1,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,2,1,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,2,1,0,0,0,0,0,0,0,0,0,0,0,0,1,2,0,0,0,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,0,0,0,2,2,0,0,0,0,0,0,0,0,0,0,0,0,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,0,1,1,1,0,2,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</t>
-  </si>
-  <si>
-    <t>209</t>
-  </si>
-  <si>
-    <t>101,101,201,201,201,201,201,201,201,201,201,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401</t>
-  </si>
-  <si>
-    <t>331,327,243,163,176,256,231,211,191,87,91,212,172,252,254,214,174,132,134,292,294,290,288,250,248,168,170,130,128,123,283,296,136</t>
+    <t>0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,1,1,1,1,1,1,1,1,1,1,0,0,0,0,0,0,0,1,1,1,1,1,1,1,1,1,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</t>
+  </si>
+  <si>
+    <t>693</t>
+  </si>
+  <si>
+    <t>401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,401,101,101,101,101,101,101,101,101,101,101,101,101,101,101,101,101</t>
+  </si>
+  <si>
+    <t>516,518,434,600,602,598,604,514,520,436,352,350,348,432,430,346,614,616,618,620,536,534,532,530,446,448,362,364,366,450,452,368,636,594,552,510,468,426,384,342,666,624,582,540,498,456,414,372</t>
   </si>
   <si>
     <t>0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,0,0,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,1,0,0,1,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,1,0,0,1,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,1,0,0,1,1,1,1,1,0,0,0,0,0,0,0,0,0,0,1,1,1,1,1,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,0,0,0,0,0,0,0,0,2,2,2,2,2,0,0,2,2,2,2,2,2,2,2,2,0,0,0,0,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,2,0,0,0,0,2,2,2,2,2,2,2,2,2,0,0,2,2,2,2,2,0,0,0,0,0,0,0,0,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,2,2,2,2,2,2,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0</t>
@@ -225,8 +228,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="0" formatCode="General"/>
+  <numFmts count="2">
     <numFmt numFmtId="0" formatCode="General"/>
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
@@ -584,7 +586,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="4" width="16" customWidth="1" style="1"/>
@@ -761,6 +763,9 @@
       </c>
     </row>
     <row r="7" ht="15">
+      <c r="A7" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="B7" s="1">
         <v>10101</v>
       </c>
@@ -771,25 +776,25 @@
         <v>6</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" s="1">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="G7" s="1">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" ht="15">
@@ -812,50 +817,19 @@
         <v>22</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" ht="15">
-      <c r="B9" s="1">
-        <v>10202</v>
-      </c>
-      <c r="C9" s="1">
-        <v>102</v>
-      </c>
-      <c r="D9" s="1">
-        <v>6</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="1">
-        <v>20</v>
-      </c>
-      <c r="G9" s="1">
-        <v>20</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1048576" ht="12.8"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -890,22 +864,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
@@ -963,25 +937,25 @@
         <v>17</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" ht="12.8">
@@ -989,13 +963,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" ht="14.9" customHeight="1">
@@ -1003,7 +977,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" ht="12.8">
@@ -1011,7 +985,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" ht="12.8">
@@ -1019,7 +993,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" ht="12.8">
@@ -1027,7 +1001,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" ht="14.15" customHeight="1">
@@ -1035,13 +1009,13 @@
         <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" ht="12.8">
@@ -1049,13 +1023,13 @@
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
